--- a/2022 data/excel_outputs/359_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/359_boothwise_data.xlsx
@@ -14,645 +14,1086 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="382">
   <si>
     <t>AC 359 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>######## #0####0##0 #### #### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ## ##### ##########</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ######### #0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ######### ##0</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### #0</t>
-  </si>
-  <si>
-    <t>######## #0#0####0##0 #####</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 #### ##0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 #### e #0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 #### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ########</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ####### ##0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ####### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #0</t>
-  </si>
-  <si>
-    <t>####0## ######</t>
-  </si>
-  <si>
-    <t>##### ##0 ######## ######</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ##### ####### #0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ##### #######e ##0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ###### ##0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ###### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##########</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #0</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ### ##0</t>
-  </si>
-  <si>
-    <t>##0##0 ##### ### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ### ##0</t>
-  </si>
-  <si>
-    <t>####0##0### #0</t>
-  </si>
-  <si>
-    <t>#### ###### ##0##0##### ########</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>#0####0##0 #### ##0</t>
-  </si>
-  <si>
-    <t>#0####0##0 #### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### #####</t>
-  </si>
-  <si>
-    <t>####0##0####e ##0</t>
-  </si>
-  <si>
-    <t>####0##0####e #0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ######e ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ######e #0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ######e ##0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ######e #0</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ######e ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ######e #0</t>
-  </si>
-  <si>
-    <t>####0##0 #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ########e ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ########e #0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ##### #0</t>
-  </si>
-  <si>
-    <t>#0####0##0 ##### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####### #0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 #### #########e ##0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 #### #########e #0</t>
-  </si>
-  <si>
-    <t>######## ######## ####e ######</t>
-  </si>
-  <si>
-    <t>######## ######## ####e #0</t>
-  </si>
-  <si>
-    <t>####0##0 ###########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####</t>
-  </si>
-  <si>
-    <t>####0 ##0 #######</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 #####e ##0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 #####e #0</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ## ########### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ## ########### #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #0</t>
-  </si>
-  <si>
-    <t>##0##0##### #####e ##0</t>
-  </si>
-  <si>
-    <t>##0##0##### #####e #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##########e ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ##########e #0</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #####</t>
-  </si>
-  <si>
-    <t>######## ### #0##0 #######e #0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ######## #0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ########e #0 ####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######</t>
-  </si>
-  <si>
-    <t>#### ### ##0##0##### ####### ##### ##########e #0</t>
-  </si>
-  <si>
-    <t>#### ### ##0##0##### ####### ##### ##########e ##0</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######## ##########e #0</t>
-  </si>
-  <si>
-    <t>####### #### ###### ##### #### ##########e ##</t>
-  </si>
-  <si>
-    <t>####### #### ###### ##### #### ##########e ##0</t>
-  </si>
-  <si>
-    <t>####### #### ###### ##### #### ##########e #0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ##########e ### ##### ## ###e ##0</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ##########e ### ##### ## ###e ####</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ##########e ### ##### ## ###e #0</t>
-  </si>
-  <si>
-    <t>####0##0 ####e #0</t>
-  </si>
-  <si>
-    <t>####0##0 ################e ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ################e #0</t>
-  </si>
-  <si>
-    <t>######## ######## #######e ##</t>
-  </si>
-  <si>
-    <t>######## ######## ########e ##0</t>
-  </si>
-  <si>
-    <t>######## ######## ########e #0</t>
-  </si>
-  <si>
-    <t>##0##0##### #######e #0</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #0</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ######</t>
-  </si>
-  <si>
-    <t>##0##0##### ######### #0</t>
-  </si>
-  <si>
-    <t>##0##0##### ######### ##</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ##### ##0</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #########e ####</t>
-  </si>
-  <si>
-    <t>####0##0 #########e #######</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ###### ########e ######</t>
-  </si>
-  <si>
-    <t>######## #0####0##0 ###### ########e #######</t>
-  </si>
-  <si>
-    <t>##### #0##0 #########e ######</t>
-  </si>
-  <si>
-    <t>##### #0##0 #########e ####</t>
-  </si>
-  <si>
-    <t>##### #0##0 #########e #######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ###e ######</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ###e #######</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ######</t>
-  </si>
-  <si>
-    <t>######## ######## #####e ####</t>
-  </si>
-  <si>
-    <t>######## ######## #####e #######</t>
-  </si>
-  <si>
-    <t>######## ######## ######e #0</t>
-  </si>
-  <si>
-    <t>####0##0 #####e ######</t>
-  </si>
-  <si>
-    <t>####0##0 #####e #######</t>
-  </si>
-  <si>
-    <t>##### ####0##0 #####</t>
-  </si>
-  <si>
-    <t>######## ######## #### ;#######ddh #0</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #####e ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #####e #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #####e ####</t>
-  </si>
-  <si>
-    <t>######## ######## ########e ######</t>
-  </si>
-  <si>
-    <t>######## ######## ########e #######</t>
-  </si>
-  <si>
-    <t>#### ##0##0##### #######e ######</t>
-  </si>
-  <si>
-    <t>#### ##0##0##### #######e ####</t>
-  </si>
-  <si>
-    <t>#### ##0##0##### #######e #######</t>
-  </si>
-  <si>
-    <t>##0##0##### #####</t>
-  </si>
-  <si>
-    <t>######## ######## ######e ######</t>
-  </si>
-  <si>
-    <t>######## ######## ######e #######</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ########e ######</t>
-  </si>
-  <si>
-    <t>####0##0 ########e ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ########e #0 ####</t>
-  </si>
-  <si>
-    <t>####0##0 ########e #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #######e ######</t>
-  </si>
-  <si>
-    <t>####0##0 #######e ###### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #######e ####### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #######e #######</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ###### ;##ddh</t>
-  </si>
-  <si>
-    <t>######## ######## ####e #######</t>
-  </si>
-  <si>
-    <t>####0##0 #####e ####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ####e ######</t>
-  </si>
-  <si>
-    <t>####0##0 ####e #######</t>
-  </si>
-  <si>
-    <t>####0##0 ######e ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######e #######</t>
-  </si>
-  <si>
-    <t>######## ######## #######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ######e ######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ######e #######</t>
-  </si>
-  <si>
-    <t>###### ### ########e ######</t>
-  </si>
-  <si>
-    <t>###### ### ########e ####</t>
-  </si>
-  <si>
-    <t>###### ### ########e #######</t>
-  </si>
-  <si>
-    <t>######## ######## ######</t>
-  </si>
-  <si>
-    <t>##0##0##### ######e ######</t>
-  </si>
-  <si>
-    <t>##0##0##### ######e ######.####</t>
-  </si>
-  <si>
-    <t>##0##0##### ######e ####</t>
-  </si>
-  <si>
-    <t>##0##0##### ######e #######.####</t>
-  </si>
-  <si>
-    <t>##0##0##### ######e #######</t>
-  </si>
-  <si>
-    <t>#### ###### #0##0 ######e ######</t>
-  </si>
-  <si>
-    <t>#### ###### #0##0 ######e ####</t>
-  </si>
-  <si>
-    <t>#### ###### #0##0 ######e #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###########e ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###########e #######</t>
-  </si>
-  <si>
-    <t>######## ######## ########</t>
-  </si>
-  <si>
-    <t>######## ######## #########</t>
-  </si>
-  <si>
-    <t>####0##0 ######e ####</t>
-  </si>
-  <si>
-    <t>####0 ##0 ###### #####</t>
-  </si>
-  <si>
-    <t>####### #0##0 ######e ######</t>
-  </si>
-  <si>
-    <t>#### ### #0##0 ######e #######</t>
-  </si>
-  <si>
-    <t>####0##0 ############e #0</t>
-  </si>
-  <si>
-    <t>####0##0 ####e ##0</t>
-  </si>
-  <si>
-    <t>####0##0 #####e ######.####</t>
-  </si>
-  <si>
-    <t>####0##0 #####e #######.####</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ##0 2e ######</t>
-  </si>
-  <si>
-    <t>####0 ##0 #### ##0 2e #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##0 ###e ######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ##0 ###e #######</t>
-  </si>
-  <si>
-    <t>##0##0##### ###e ######</t>
-  </si>
-  <si>
-    <t>##0##0##### ###e #######</t>
-  </si>
-  <si>
-    <t>####0##0 ###e ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###e ######.####</t>
-  </si>
-  <si>
-    <t>####0##0 ###e #######.####</t>
-  </si>
-  <si>
-    <t>####0##0 ###e #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0 ###</t>
-  </si>
-  <si>
-    <t>######### #0##0 ###</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0 ### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0 ### ######.####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0 ### #######.####</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##0 ### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #######</t>
-  </si>
-  <si>
-    <t>##### ##0 ######## #####e ;##0ddh</t>
-  </si>
-  <si>
-    <t>##### ##0 ######## #####e ;#0ddh</t>
-  </si>
-  <si>
-    <t>####0##0 ############e ######</t>
-  </si>
-  <si>
-    <t>####0##0 ############e #######</t>
-  </si>
-  <si>
-    <t>####0##0 ############e ####</t>
-  </si>
-  <si>
-    <t>######## ######## ###########e ######</t>
-  </si>
-  <si>
-    <t>######## ######## ###########e #######</t>
-  </si>
-  <si>
-    <t>######## ######## #####</t>
-  </si>
-  <si>
-    <t>##0##0##### ##### #### ##### ##0 #####</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##0</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #0</t>
+    <t>P.P.DUHA ,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.DUHA,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.DUHA, SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.BIHARA NO. 1</t>
+  </si>
+  <si>
+    <t>P.P.BIHARA NO. 2</t>
+  </si>
+  <si>
+    <t>P.P.BHARTI KA PURWA</t>
+  </si>
+  <si>
+    <t>DUHABIHARA JR.H.S..DUHA</t>
+  </si>
+  <si>
+    <t>BIHARA,WEST JR.H.S.DUHA BIHARA,</t>
+  </si>
+  <si>
+    <t>EAST JR.H.S.KATHAURA,</t>
+  </si>
+  <si>
+    <t>NORTH JR.H.S.KATHAURA,</t>
+  </si>
+  <si>
+    <t>MIDDLE JR.H.S.KATHAURA,</t>
+  </si>
+  <si>
+    <t>SOUTH P.P.KATHAURA</t>
+  </si>
+  <si>
+    <t>P.P.JAMUI,EAST</t>
+  </si>
+  <si>
+    <t>P.P.JAMUI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.BARHUCHA</t>
+  </si>
+  <si>
+    <t>P.P.MUIYA</t>
+  </si>
+  <si>
+    <t>P.P.DUBAULI</t>
+  </si>
+  <si>
+    <t>INDRACHAK P.P.BHIMHAR</t>
+  </si>
+  <si>
+    <t>P.P.DHORIDIH</t>
+  </si>
+  <si>
+    <t>P.P.HADSAR</t>
+  </si>
+  <si>
+    <t>P.P.KUNDIDIH</t>
+  </si>
+  <si>
+    <t>P.P.MALDAH</t>
+  </si>
+  <si>
+    <t>P.M.V. TILAULI</t>
+  </si>
+  <si>
+    <t>P.P.HARNATAR</t>
+  </si>
+  <si>
+    <t>DYALPUR,NORTH P.P.HARNATAR</t>
+  </si>
+  <si>
+    <t>DYALPUR,SOUTH JR.H.S.NAWANAGAR,E</t>
+  </si>
+  <si>
+    <t>AST JR.H.S.NAWANAGAR,W</t>
+  </si>
+  <si>
+    <t>EST P.P.NAWANAGAR</t>
+  </si>
+  <si>
+    <t>P.P.MALEJI</t>
+  </si>
+  <si>
+    <t>P.P.TURKWALIA</t>
+  </si>
+  <si>
+    <t>P.P.MAJHAWALIA,</t>
+  </si>
+  <si>
+    <t>EAST P.P.MAJHAWALIA,</t>
+  </si>
+  <si>
+    <t>WEST P.P.MALWAR</t>
+  </si>
+  <si>
+    <t>P.P.AKASAR</t>
+  </si>
+  <si>
+    <t>P.P.RUDRAWAR, EAST</t>
+  </si>
+  <si>
+    <t>P.P.RUDRAWAR, WEST</t>
+  </si>
+  <si>
+    <t>P.P.USURI</t>
+  </si>
+  <si>
+    <t>JR.H.S.KOTH,EAST</t>
+  </si>
+  <si>
+    <t>JR.H.S.KOTH,WEST</t>
+  </si>
+  <si>
+    <t>P.P.KOTH,EAST</t>
+  </si>
+  <si>
+    <t>P.P.KOTH,WEST</t>
+  </si>
+  <si>
+    <t>P.P.RASARI</t>
+  </si>
+  <si>
+    <t>P.P.MATURI</t>
+  </si>
+  <si>
+    <t>P.P.HUSENPUR,EAST</t>
+  </si>
+  <si>
+    <t>P.P.HUSENPUR,WEST</t>
+  </si>
+  <si>
+    <t>SANT RAVIDAS</t>
+  </si>
+  <si>
+    <t>JR.H.S.HUSENPUR P.P.JAMALPUR</t>
+  </si>
+  <si>
+    <t>KANYA</t>
+  </si>
+  <si>
+    <t>P.P.CHADI,EAST KANYA</t>
+  </si>
+  <si>
+    <t>P.P.CHADI,WEST P.P.KATGHARA JAMIN</t>
+  </si>
+  <si>
+    <t>KATGHARA P.P.TENDUWA</t>
+  </si>
+  <si>
+    <t>P.P.TENDUWA</t>
+  </si>
+  <si>
+    <t>JR.H.S.BAGHUDI,</t>
+  </si>
+  <si>
+    <t>NORTH JR.H.S.BAGHUDI,</t>
+  </si>
+  <si>
+    <t>SOUTH P.P.KARSI</t>
+  </si>
+  <si>
+    <t>P.P.HARDIA JAMIN</t>
+  </si>
+  <si>
+    <t>HARDIA P.P.DEOKALI, EAST</t>
+  </si>
+  <si>
+    <t>P.P.DEOKALI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.SARION MANOVIR</t>
+  </si>
+  <si>
+    <t>P.P.BARMADIA</t>
+  </si>
+  <si>
+    <t>P.P.BELSARI</t>
+  </si>
+  <si>
+    <t>P.P.BHARTHAON</t>
+  </si>
+  <si>
+    <t>P.P.LAUHAR NEW</t>
+  </si>
+  <si>
+    <t>BULDING P.P.KODAI</t>
+  </si>
+  <si>
+    <t>P.P.SIKIA,EAST</t>
+  </si>
+  <si>
+    <t>P.P.SIKIA,WEST</t>
+  </si>
+  <si>
+    <t>P.P.KHATANGI MATH</t>
+  </si>
+  <si>
+    <t>RAMGIR P.P.JAJAULI CHAK</t>
+  </si>
+  <si>
+    <t>RAJMAN,SOUTH P.P.JAJAULI CHAK</t>
+  </si>
+  <si>
+    <t>RAJMAN,NORTH KANYA.P.P.JAJAULI</t>
+  </si>
+  <si>
+    <t>CHAK RAJMAN P.P.MAHARO</t>
+  </si>
+  <si>
+    <t>P.P.BASTI</t>
+  </si>
+  <si>
+    <t>BUZURG,EAST P.P.BASTI</t>
+  </si>
+  <si>
+    <t>BUZURG,WEST P.P.ISHAR PITHAPATTI</t>
+  </si>
+  <si>
+    <t>JR.H.S.ISHAR</t>
+  </si>
+  <si>
+    <t>PITHAPATTI P.M.V.AKAIL,EAST</t>
+  </si>
+  <si>
+    <t>P.M.V.AKAIL,WEST</t>
+  </si>
+  <si>
+    <t>P.P.GAURAMADANPUR</t>
+  </si>
+  <si>
+    <t>A P.P.KHAIRA CHAK</t>
+  </si>
+  <si>
+    <t>HETIM P.P.UCHAWAR</t>
+  </si>
+  <si>
+    <t>P.P.RAMPUR KATARAI</t>
+  </si>
+  <si>
+    <t>P.P.SONVARSA</t>
+  </si>
+  <si>
+    <t>P.P.SARANI</t>
+  </si>
+  <si>
+    <t>P.P.MUDERA</t>
+  </si>
+  <si>
+    <t>P.P.BHATI,EAST</t>
+  </si>
+  <si>
+    <t>P.P.BHATI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.GAJIPAKAD</t>
+  </si>
+  <si>
+    <t>P.P.CHAKPREMA URF</t>
+  </si>
+  <si>
+    <t>BHATAWACHAK P.P.KARMAUTA, EAST</t>
+  </si>
+  <si>
+    <t>P.P.KARMAUTA, NEW</t>
+  </si>
+  <si>
+    <t>BUILDING P.P.CHAK</t>
+  </si>
+  <si>
+    <t>PURUSHOTTIM P.P.LILKAR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.LILKAR,SOUTH</t>
+  </si>
+  <si>
+    <t>JR.H.S.LILKAR</t>
+  </si>
+  <si>
+    <t>P.P.LAKSHMIPUR</t>
+  </si>
+  <si>
+    <t>P.P.MATHIA(LILKAR)</t>
+  </si>
+  <si>
+    <t>P.P.SISOTAR,EAST</t>
+  </si>
+  <si>
+    <t>P.P.SISOTAR,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.SISOTAR,WEST</t>
+  </si>
+  <si>
+    <t>JR.H.S.SISOTAR,</t>
+  </si>
+  <si>
+    <t>NORTH JR.H.S.SISOTAR,MIDDL</t>
+  </si>
+  <si>
+    <t>E JR.H.S.SISOTAR,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.BASARIKPUR,NORT</t>
+  </si>
+  <si>
+    <t>H P.P.BASARIKPUR,MIDD</t>
+  </si>
+  <si>
+    <t>LE P.P.BASARIKPUR,SOUT</t>
+  </si>
+  <si>
+    <t>H P.P.GOSAIPUR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.GOSAIPUR,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.GOSAIPUR,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.BADAMAFI,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.BADAMAFI</t>
+  </si>
+  <si>
+    <t>P.P.BADAMAFI,EAST</t>
+  </si>
+  <si>
+    <t>P.P.BADAMAFI,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.BADAMAFI,NEW</t>
+  </si>
+  <si>
+    <t>BUILDING HAJARAT ASI</t>
+  </si>
+  <si>
+    <t>JR.H.S.MO.GANDHI HAJARAT ASI</t>
+  </si>
+  <si>
+    <t>JR.H.S.MO.GANDHI KANYA P.P.HOSPITAL</t>
+  </si>
+  <si>
+    <t>SIKANDARPUR KANYA P.P.HOSPITAL</t>
+  </si>
+  <si>
+    <t>SIKANDARPUR SARSWATI S.MANDIR</t>
+  </si>
+  <si>
+    <t>POLICE CHAUKI SARSWATI S.MANDIR</t>
+  </si>
+  <si>
+    <t>POLICE CHAUKI P.P.SIKANDARPUR</t>
+  </si>
+  <si>
+    <t>NEAR OF DAK BANGLA P.P.SIKANDARPUR</t>
+  </si>
+  <si>
+    <t>NEAR OF DAK P.P.SIKANDARPUR</t>
+  </si>
+  <si>
+    <t>NEAR OF DAK BANGLA P.P.CHAKBALDEO</t>
+  </si>
+  <si>
+    <t>P.P.KHARID NORTH</t>
+  </si>
+  <si>
+    <t>P.P.KHARID SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.PURUSHOTTAMPAT</t>
+  </si>
+  <si>
+    <t>TI, EAST P.P.PURUSHOTTAMPAT</t>
+  </si>
+  <si>
+    <t>TI,WEST P.P.NIPANIA SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.NIPANIA NORTH</t>
+  </si>
+  <si>
+    <t>P.P.BIJULIPUR</t>
+  </si>
+  <si>
+    <t>JR.H.S.KAJIPUR,NORTH</t>
+  </si>
+  <si>
+    <t>JR.H.S.KAJIPUR,SOUTH</t>
+  </si>
+  <si>
+    <t>JR.H.S.KAJIPUR,MIDDL</t>
+  </si>
+  <si>
+    <t>E P.P.MUSTFABAD</t>
+  </si>
+  <si>
+    <t>P.P.CHAK HAJI URF</t>
+  </si>
+  <si>
+    <t>SHEKHPUR JR.H.S.GANGKISHOR,N</t>
+  </si>
+  <si>
+    <t>ORTH JR.H.S.GANGKISHOR,N</t>
+  </si>
+  <si>
+    <t>ORTH P.P.CHAKKHAN</t>
+  </si>
+  <si>
+    <t>P.P.KISHOR</t>
+  </si>
+  <si>
+    <t>CHETAN,EAST P.P.KISHOR</t>
+  </si>
+  <si>
+    <t>CHETAN,WEST P.P.SIWANKALA,EAST</t>
+  </si>
+  <si>
+    <t>P.P.SIWANKALA,WEST</t>
+  </si>
+  <si>
+    <t>P.P.HARDIA</t>
+  </si>
+  <si>
+    <t>SIWANKALA,NORTH P.P.HARDIA</t>
+  </si>
+  <si>
+    <t>SIWANKALA,SOUTH ADARSH</t>
+  </si>
+  <si>
+    <t>I.C.SIWANKALA ADARSH</t>
+  </si>
+  <si>
+    <t>I.C.SIWANKALA P.P.BICHHI BOJH</t>
+  </si>
+  <si>
+    <t>P.P.PANDAH</t>
+  </si>
+  <si>
+    <t>P.P.PANDAH,NEW P.P.ITAHI</t>
+  </si>
+  <si>
+    <t>P.P.KIKODHA,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.KIKODHA,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.BHADIKARA</t>
+  </si>
+  <si>
+    <t>P.P.BANHARA</t>
+  </si>
+  <si>
+    <t>KANYA P.P.BANHARA</t>
+  </si>
+  <si>
+    <t>P.P.SANDWAPUR</t>
+  </si>
+  <si>
+    <t>P.P.LAKHANPAR,NORT</t>
+  </si>
+  <si>
+    <t>H P.P.LAKHANPAR,SOUT</t>
+  </si>
+  <si>
+    <t>H P.P.MANGUWARPAR</t>
+  </si>
+  <si>
+    <t>URF DANKIGANJ P.P.NANHUL</t>
+  </si>
+  <si>
+    <t>P.P.NANHUL</t>
+  </si>
+  <si>
+    <t>P.P.CHADWA-</t>
+  </si>
+  <si>
+    <t>BARWA,EAST P.P.CHADWA-</t>
+  </si>
+  <si>
+    <t>BARWA,WEST P.P.CHADWA-BARWA</t>
+  </si>
+  <si>
+    <t>JR.H.S. FULWARIA</t>
+  </si>
+  <si>
+    <t>DASHARATH</t>
+  </si>
+  <si>
+    <t>JR.H.S.BACHHAPAR, DASHARATH</t>
+  </si>
+  <si>
+    <t>JR.H.S.BANCHHAPAR, DASHARATH</t>
+  </si>
+  <si>
+    <t>JR.H.S.BACHHAPAR, P.P.RAMAPAR</t>
+  </si>
+  <si>
+    <t>P.P.KADSAR,EAST</t>
+  </si>
+  <si>
+    <t>JR.H.S.BAHERI</t>
+  </si>
+  <si>
+    <t>P.P.JETHWAR NAYA</t>
+  </si>
+  <si>
+    <t>BHAVAN P.P.JETHWAR NAYA</t>
+  </si>
+  <si>
+    <t>BHAVAN P.P.MARWATIA</t>
+  </si>
+  <si>
+    <t>P.P.SONPURWA</t>
+  </si>
+  <si>
+    <t>JR.H.S.ARAJI KARIYAR</t>
+  </si>
+  <si>
+    <t>P.P.MASUMPUR, EAST</t>
+  </si>
+  <si>
+    <t>P.P.MASUMPUR, EAST-</t>
+  </si>
+  <si>
+    <t>MIDDLE P.P.MASUMPUR, WEST-</t>
+  </si>
+  <si>
+    <t>MIDDLE P.P.MASUMPUR,WEST</t>
+  </si>
+  <si>
+    <t>P.P.KAITHWALI</t>
+  </si>
+  <si>
+    <t>P.P.SASANA AHALU</t>
+  </si>
+  <si>
+    <t>P.P.BALUPUR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.BALUPUR,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.BALUPUR,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.MAHATHAPAR,EAS</t>
+  </si>
+  <si>
+    <t>T P.P.MAHATHAPAR,WES</t>
+  </si>
+  <si>
+    <t>T P.P.CHANDAIR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.CHANDAIR,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.SARKANDA</t>
+  </si>
+  <si>
+    <t>P.P.BAHADURA,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.BAHADURA,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.ASANA,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.ASANA,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.PILUI</t>
+  </si>
+  <si>
+    <t>P.P.PILUI ATIRIKT</t>
+  </si>
+  <si>
+    <t>P.P.DURAUDHA</t>
+  </si>
+  <si>
+    <t>P.P.BHAGIPUR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.BHAGIPUR,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.AJAUR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.AJAUR,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.HATHAUJ,EAST</t>
+  </si>
+  <si>
+    <t>P.P.HATHAUJ,WEST</t>
+  </si>
+  <si>
+    <t>JR.H.S.HATHAUJ,EAST</t>
+  </si>
+  <si>
+    <t>JR.H.S.HATHAUJ,WEST</t>
+  </si>
+  <si>
+    <t>P.P.AJANERA,EAST</t>
+  </si>
+  <si>
+    <t>P.P.AJANERA,WEST</t>
+  </si>
+  <si>
+    <t>P.P.GODAWARA</t>
+  </si>
+  <si>
+    <t>P.P.AHIRAULI</t>
+  </si>
+  <si>
+    <t>TIWARI,EAST P.P.PRANPUR</t>
+  </si>
+  <si>
+    <t>P.P.JIGIRSAD,EAST</t>
+  </si>
+  <si>
+    <t>P.P.BANKATA,WEST</t>
+  </si>
+  <si>
+    <t>P. BHAWAN</t>
+  </si>
+  <si>
+    <t>JIGIRSAD,NORTH P. BHAWAN</t>
+  </si>
+  <si>
+    <t>JIGIRSAD,SOUTH P.P.AKHAINI</t>
+  </si>
+  <si>
+    <t>P.P.BADASARI</t>
+  </si>
+  <si>
+    <t>JR.H.S.KHEJURI,EAST</t>
+  </si>
+  <si>
+    <t>JR.H.S.KHEJURI,MIDDL</t>
+  </si>
+  <si>
+    <t>E JR.H.S.KHEJURI,MIDDL</t>
+  </si>
+  <si>
+    <t>E JR.H.S.KHEJURI,WEST</t>
+  </si>
+  <si>
+    <t>SHRI AMARNATH</t>
+  </si>
+  <si>
+    <t>I.C.KHEJURI,EAST SHRI AMARNATH</t>
+  </si>
+  <si>
+    <t>I.C.KHEJURI,MIDDLE SHRI AMARNATH</t>
+  </si>
+  <si>
+    <t>I.C.KHEJURI,WEST P.P.FIROJPUR</t>
+  </si>
+  <si>
+    <t>P.P.BANKATAKALA</t>
+  </si>
+  <si>
+    <t>P.P.BHUDADIH,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.BHUDADIH,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.KAUDIA</t>
+  </si>
+  <si>
+    <t>P.P.JANUAN,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.JANUAN,SOUTH</t>
+  </si>
+  <si>
+    <t>P.P.CHAK USARAILA</t>
+  </si>
+  <si>
+    <t>P.P.CHAK BAHAUDDIN</t>
+  </si>
+  <si>
+    <t>P.P.JUGESARA</t>
+  </si>
+  <si>
+    <t>P.P.SLEMPUR</t>
+  </si>
+  <si>
+    <t>P.P.SHIDHAULI</t>
+  </si>
+  <si>
+    <t>P.P.GOPALPUR</t>
+  </si>
+  <si>
+    <t>P.P.GAURI</t>
+  </si>
+  <si>
+    <t>P.P.PRASADPUR</t>
+  </si>
+  <si>
+    <t>P.P.MUJAHI</t>
+  </si>
+  <si>
+    <t>P.P.TANDWA</t>
+  </si>
+  <si>
+    <t>P.P.NAHILAPAR</t>
+  </si>
+  <si>
+    <t>P.P.BABHANAULI</t>
+  </si>
+  <si>
+    <t>P.P.SAHULAI,EAST</t>
+  </si>
+  <si>
+    <t>P.P.SAHULAI,WEST</t>
+  </si>
+  <si>
+    <t>P.P.SAHULAI,MIDDLE</t>
+  </si>
+  <si>
+    <t>SHRINATH</t>
+  </si>
+  <si>
+    <t>I.C.SAHULAI,EAST SHRINATH</t>
+  </si>
+  <si>
+    <t>I.C.SAHULAI,WEST P.P.GARHMALPUR,EAS</t>
+  </si>
+  <si>
+    <t>T P.P.GARHMALPUR,WES</t>
+  </si>
+  <si>
+    <t>T P.P.RATASI</t>
+  </si>
+  <si>
+    <t>MEHMAPUR,NORTH P.P.RATASI</t>
+  </si>
+  <si>
+    <t>MEHMAPUR,SOUTH P.P.UKCHHI</t>
+  </si>
+  <si>
+    <t>P.P.MISHRAULI</t>
+  </si>
+  <si>
+    <t>P.P.DOGHARA</t>
+  </si>
+  <si>
+    <t>P.P.PAKARI</t>
+  </si>
+  <si>
+    <t>P.P.PAKARI NO. 2</t>
+  </si>
+  <si>
+    <t>JR.H.S.PAKARI</t>
+  </si>
+  <si>
+    <t>P.P.PAHARAJPUR, EAST</t>
+  </si>
+  <si>
+    <t>P.P.PAHARAJPUR,WEST</t>
+  </si>
+  <si>
+    <t>P.P.USASA</t>
+  </si>
+  <si>
+    <t>MU.PUR,NORTH P.P.USASA</t>
+  </si>
+  <si>
+    <t>MU.PUR,SOUTH P.P.USASA</t>
+  </si>
+  <si>
+    <t>MU.PUR,EAST P.P.JIMEECHAK</t>
+  </si>
+  <si>
+    <t>JR.H.S.PUR</t>
+  </si>
+  <si>
+    <t>P.P.PUR,NORTH</t>
+  </si>
+  <si>
+    <t>P.P.PUR,MIDDLE</t>
+  </si>
+  <si>
+    <t>P.P.KACHILA MU.PUR</t>
+  </si>
+  <si>
+    <t>P.P.CHAKRA</t>
+  </si>
+  <si>
+    <t>HARBANSBABA</t>
+  </si>
+  <si>
+    <t>I.C.PUR P.P.GAURANIA</t>
+  </si>
+  <si>
+    <t>P.P.DHADASRA</t>
+  </si>
+  <si>
+    <t>P.P.JAGDARA</t>
+  </si>
+  <si>
+    <t>MU.PUR,WEST P.P.JAGDARA</t>
+  </si>
+  <si>
+    <t>MU.PUR,MIDDLE P.P.JAGDARA</t>
+  </si>
+  <si>
+    <t>MU.PUR,MIDDLE P.P.SONADIH,EAST</t>
+  </si>
+  <si>
+    <t>P.P.SONADIH,WEST</t>
+  </si>
+  <si>
+    <t>P.P.KHABASPUR</t>
+  </si>
+  <si>
+    <t>P.P.SARAYA</t>
+  </si>
+  <si>
+    <t>P.P.MEULIKNASPUR,EA</t>
+  </si>
+  <si>
+    <t>ST P.P.MEULIKNASPUR,W</t>
+  </si>
+  <si>
+    <t>EST P.P.MEULIKNASPUR,W</t>
+  </si>
+  <si>
+    <t>EST P.P.RAKSADENIA</t>
+  </si>
+  <si>
+    <t>P.P.VISHAHAR</t>
+  </si>
+  <si>
+    <t>P.P.KALYANDEHARA</t>
+  </si>
+  <si>
+    <t>P.P.KHADASARA,NORT</t>
+  </si>
+  <si>
+    <t>H P.P.KHADASARA,MIDD</t>
+  </si>
+  <si>
+    <t>LE P.P.KHADASARA,MIDD</t>
+  </si>
+  <si>
+    <t>LE P.P.SARDAHI</t>
+  </si>
+  <si>
+    <t>JR.H.S.TOLA BANATI</t>
+  </si>
+  <si>
+    <t>MU.KHADSARA P.P.KHADASARA,H.B.</t>
+  </si>
+  <si>
+    <t>P.P.KHADASARA,H.B.</t>
+  </si>
+  <si>
+    <t>P.P.RUPWAR TWAYAF</t>
+  </si>
+  <si>
+    <t>P.P.CHAWARI</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM NO. 313</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM NO. 314</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM NO. 315</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM NO. 316</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM NO. 317</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM NO. 318</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 319</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 320</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 321</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 322</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 323</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 324</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 325</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 326</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 327</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 328</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 329</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 330</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 331</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 332</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 333</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 334</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 335</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 336</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 337</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 338</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 339</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 340</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 341</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 342</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 343</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 344</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 345</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 346</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 347</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 348</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 349</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 350</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 351</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 352</t>
+  </si>
+  <si>
+    <t>P.P.HARIPUR ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 353</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -725,8 +1166,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -742,7 +1191,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -750,12 +1199,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1054,82 +1521,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
+        <v>360</v>
       </c>
       <c r="D2" t="s">
-        <v>214</v>
+        <v>361</v>
       </c>
       <c r="E2" t="s">
-        <v>215</v>
+        <v>362</v>
       </c>
       <c r="F2" t="s">
-        <v>216</v>
+        <v>363</v>
       </c>
       <c r="G2" t="s">
-        <v>217</v>
+        <v>364</v>
       </c>
       <c r="H2" t="s">
-        <v>218</v>
+        <v>365</v>
       </c>
       <c r="I2" t="s">
-        <v>219</v>
+        <v>366</v>
       </c>
       <c r="J2" t="s">
-        <v>220</v>
+        <v>367</v>
       </c>
       <c r="K2" t="s">
-        <v>221</v>
+        <v>368</v>
       </c>
       <c r="L2" t="s">
-        <v>222</v>
+        <v>369</v>
       </c>
       <c r="M2" t="s">
-        <v>223</v>
+        <v>370</v>
       </c>
       <c r="N2" t="s">
-        <v>224</v>
+        <v>371</v>
       </c>
       <c r="O2" t="s">
-        <v>225</v>
+        <v>372</v>
       </c>
       <c r="P2" t="s">
-        <v>226</v>
+        <v>373</v>
       </c>
       <c r="Q2" t="s">
-        <v>227</v>
+        <v>374</v>
       </c>
       <c r="R2" t="s">
-        <v>228</v>
+        <v>375</v>
       </c>
       <c r="S2" t="s">
-        <v>229</v>
+        <v>376</v>
       </c>
       <c r="T2" t="s">
-        <v>230</v>
+        <v>377</v>
       </c>
       <c r="U2" t="s">
-        <v>231</v>
+        <v>378</v>
       </c>
       <c r="V2" t="s">
-        <v>232</v>
+        <v>379</v>
       </c>
       <c r="W2" t="s">
-        <v>233</v>
+        <v>380</v>
       </c>
       <c r="X2" t="s">
-        <v>234</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1137,7 +1673,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1060</v>
@@ -1211,7 +1747,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>881</v>
@@ -1285,7 +1821,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>862</v>
@@ -1359,7 +1895,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>835</v>
@@ -1433,7 +1969,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>846</v>
@@ -1507,7 +2043,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>969</v>
@@ -1581,7 +2117,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>690</v>
@@ -1655,7 +2191,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>1027</v>
@@ -1729,7 +2265,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>1189</v>
@@ -1803,7 +2339,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>1191</v>
@@ -1877,7 +2413,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>1153</v>
@@ -1951,7 +2487,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>883</v>
@@ -2025,7 +2561,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>925</v>
@@ -2099,7 +2635,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>1006</v>
@@ -2173,7 +2709,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1029</v>
@@ -2247,7 +2783,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>599</v>
@@ -2321,7 +2857,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>815</v>
@@ -2395,7 +2931,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>753</v>
@@ -2469,7 +3005,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>717</v>
@@ -2543,7 +3079,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>656</v>
@@ -2617,7 +3153,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>560</v>
@@ -2691,7 +3227,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>828</v>
@@ -2765,7 +3301,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>575</v>
@@ -2839,7 +3375,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>769</v>
@@ -2913,7 +3449,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>1029</v>
@@ -2987,7 +3523,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>783</v>
@@ -3061,7 +3597,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>907</v>
@@ -3135,7 +3671,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>827</v>
@@ -3209,7 +3745,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>866</v>
@@ -3283,7 +3819,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>982</v>
@@ -3357,7 +3893,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>912</v>
@@ -3431,7 +3967,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>534</v>
@@ -3505,7 +4041,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>351</v>
@@ -3579,7 +4115,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>1152</v>
@@ -3653,7 +4189,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>744</v>
@@ -3727,7 +4263,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>777</v>
@@ -3801,7 +4337,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>842</v>
@@ -3875,7 +4411,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>710</v>
@@ -3949,7 +4485,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>1164</v>
@@ -4023,7 +4559,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>915</v>
@@ -4097,7 +4633,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>564</v>
@@ -4171,7 +4707,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="C44">
         <v>917</v>
@@ -4245,7 +4781,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="C45">
         <v>754</v>
@@ -4319,7 +4855,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>825</v>
@@ -4393,7 +4929,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>923</v>
@@ -4467,7 +5003,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>847</v>
@@ -4541,7 +5077,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>941</v>
@@ -4615,7 +5151,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>1101</v>
@@ -4689,7 +5225,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>799</v>
@@ -4763,7 +5299,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>929</v>
@@ -4837,7 +5373,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>1034</v>
@@ -4911,7 +5447,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C54">
         <v>940</v>
@@ -4985,7 +5521,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>775</v>
@@ -5059,7 +5595,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>825</v>
@@ -5133,7 +5669,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>845</v>
@@ -5207,7 +5743,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>1036</v>
@@ -5281,7 +5817,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="C59">
         <v>548</v>
@@ -5355,7 +5891,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="C60">
         <v>1032</v>
@@ -5429,7 +5965,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>964</v>
@@ -5503,7 +6039,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>678</v>
@@ -5577,7 +6113,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>627</v>
@@ -5651,7 +6187,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>686</v>
@@ -5725,7 +6261,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C65">
         <v>630</v>
@@ -5799,7 +6335,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>1154</v>
@@ -5873,7 +6409,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="C67">
         <v>1051</v>
@@ -5947,7 +6483,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>774</v>
@@ -6021,7 +6557,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>659</v>
@@ -6095,7 +6631,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>516</v>
@@ -6169,7 +6705,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>1049</v>
@@ -6243,7 +6779,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>919</v>
@@ -6317,7 +6853,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>653</v>
@@ -6391,7 +6927,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>635</v>
@@ -6465,7 +7001,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>685</v>
@@ -6539,7 +7075,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="C76">
         <v>955</v>
@@ -6613,7 +7149,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>826</v>
@@ -6687,7 +7223,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>804</v>
@@ -6761,7 +7297,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>664</v>
@@ -6835,7 +7371,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>749</v>
@@ -6909,7 +7445,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>916</v>
@@ -6983,7 +7519,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>1117</v>
@@ -7057,7 +7593,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>880</v>
@@ -7131,7 +7667,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>749</v>
@@ -7205,7 +7741,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>1002</v>
@@ -7279,7 +7815,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>704</v>
@@ -7353,7 +7889,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>1118</v>
@@ -7427,7 +7963,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>1116</v>
@@ -7501,7 +8037,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>877</v>
@@ -7575,7 +8111,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>894</v>
@@ -7649,7 +8185,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>812</v>
@@ -7723,7 +8259,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>65</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>662</v>
@@ -7797,7 +8333,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="C93">
         <v>603</v>
@@ -7871,7 +8407,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>1034</v>
@@ -7945,7 +8481,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>364</v>
@@ -8019,7 +8555,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>610</v>
@@ -8093,7 +8629,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>629</v>
@@ -8167,7 +8703,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="C98">
         <v>842</v>
@@ -8241,7 +8777,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="C99">
         <v>992</v>
@@ -8315,7 +8851,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C100">
         <v>755</v>
@@ -8389,7 +8925,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="C101">
         <v>856</v>
@@ -8463,7 +8999,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="C102">
         <v>937</v>
@@ -8537,7 +9073,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>46</v>
+        <v>123</v>
       </c>
       <c r="C103">
         <v>849</v>
@@ -8611,7 +9147,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="C104">
         <v>882</v>
@@ -8685,7 +9221,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="C105">
         <v>586</v>
@@ -8759,7 +9295,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C106">
         <v>654</v>
@@ -8833,7 +9369,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="C107">
         <v>673</v>
@@ -8907,7 +9443,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="C108">
         <v>1165</v>
@@ -8981,7 +9517,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="C109">
         <v>917</v>
@@ -9055,7 +9591,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="C110">
         <v>675</v>
@@ -9129,7 +9665,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="C111">
         <v>838</v>
@@ -9203,7 +9739,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="C112">
         <v>1022</v>
@@ -9277,7 +9813,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="C113">
         <v>1074</v>
@@ -9351,7 +9887,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="C114">
         <v>1141</v>
@@ -9425,7 +9961,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="C115">
         <v>1133</v>
@@ -9499,7 +10035,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="C116">
         <v>1162</v>
@@ -9573,7 +10109,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="C117">
         <v>1068</v>
@@ -9647,7 +10183,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="C118">
         <v>1094</v>
@@ -9721,7 +10257,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="C119">
         <v>1092</v>
@@ -9795,7 +10331,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="C120">
         <v>1096</v>
@@ -9869,7 +10405,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="C121">
         <v>914</v>
@@ -9943,7 +10479,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="C122">
         <v>1048</v>
@@ -10017,7 +10553,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="C123">
         <v>1161</v>
@@ -10091,7 +10627,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="C124">
         <v>1134</v>
@@ -10165,7 +10701,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="C125">
         <v>592</v>
@@ -10239,7 +10775,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="C126">
         <v>654</v>
@@ -10313,7 +10849,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="C127">
         <v>1136</v>
@@ -10387,7 +10923,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="C128">
         <v>1132</v>
@@ -10461,7 +10997,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="C129">
         <v>1051</v>
@@ -10535,7 +11071,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="C130">
         <v>1180</v>
@@ -10609,7 +11145,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>82</v>
+        <v>147</v>
       </c>
       <c r="C131">
         <v>1151</v>
@@ -10683,7 +11219,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>83</v>
+        <v>148</v>
       </c>
       <c r="C132">
         <v>1151</v>
@@ -10757,7 +11293,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="C133">
         <v>1203</v>
@@ -10831,7 +11367,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C134">
         <v>1114</v>
@@ -10905,7 +11441,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="C135">
         <v>980</v>
@@ -10979,7 +11515,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="C136">
         <v>746</v>
@@ -11053,7 +11589,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="C137">
         <v>1100</v>
@@ -11127,7 +11663,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
       <c r="C138">
         <v>1125</v>
@@ -11201,7 +11737,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="C139">
         <v>819</v>
@@ -11275,7 +11811,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="C140">
         <v>1023</v>
@@ -11349,7 +11885,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>88</v>
+        <v>157</v>
       </c>
       <c r="C141">
         <v>1032</v>
@@ -11423,7 +11959,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="C142">
         <v>965</v>
@@ -11497,7 +12033,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="C143">
         <v>982</v>
@@ -11571,7 +12107,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="C144">
         <v>993</v>
@@ -11645,7 +12181,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="C145">
         <v>879</v>
@@ -11719,7 +12255,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>37</v>
+        <v>162</v>
       </c>
       <c r="C146">
         <v>1157</v>
@@ -11793,7 +12329,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="C147">
         <v>1233</v>
@@ -11867,7 +12403,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="C148">
         <v>1179</v>
@@ -11941,7 +12477,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>93</v>
+        <v>165</v>
       </c>
       <c r="C149">
         <v>1112</v>
@@ -12015,7 +12551,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="C150">
         <v>1101</v>
@@ -12089,7 +12625,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="C151">
         <v>985</v>
@@ -12163,7 +12699,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>95</v>
+        <v>168</v>
       </c>
       <c r="C152">
         <v>1039</v>
@@ -12237,7 +12773,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="C153">
         <v>732</v>
@@ -12311,7 +12847,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="C154">
         <v>684</v>
@@ -12385,7 +12921,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="C155">
         <v>1119</v>
@@ -12459,7 +12995,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>98</v>
+        <v>171</v>
       </c>
       <c r="C156">
         <v>1036</v>
@@ -12533,7 +13069,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C157">
         <v>873</v>
@@ -12607,7 +13143,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="C158">
         <v>816</v>
@@ -12681,7 +13217,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="C159">
         <v>756</v>
@@ -12755,7 +13291,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="C160">
         <v>994</v>
@@ -12829,7 +13365,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="C161">
         <v>946</v>
@@ -12903,7 +13439,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="C162">
         <v>692</v>
@@ -12977,7 +13513,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="C163">
         <v>1065</v>
@@ -13051,7 +13587,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="C164">
         <v>563</v>
@@ -13125,7 +13661,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="C165">
         <v>1163</v>
@@ -13199,7 +13735,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>106</v>
+        <v>179</v>
       </c>
       <c r="C166">
         <v>1141</v>
@@ -13273,7 +13809,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>107</v>
+        <v>180</v>
       </c>
       <c r="C167">
         <v>592</v>
@@ -13347,7 +13883,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>105</v>
+        <v>181</v>
       </c>
       <c r="C168">
         <v>895</v>
@@ -13421,7 +13957,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>108</v>
+        <v>182</v>
       </c>
       <c r="C169">
         <v>714</v>
@@ -13495,7 +14031,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="C170">
         <v>938</v>
@@ -13569,7 +14105,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="C171">
         <v>1176</v>
@@ -13643,7 +14179,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="C172">
         <v>1078</v>
@@ -13717,7 +14253,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="C173">
         <v>896</v>
@@ -13791,7 +14327,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>113</v>
+        <v>187</v>
       </c>
       <c r="C174">
         <v>1030</v>
@@ -13865,7 +14401,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>114</v>
+        <v>188</v>
       </c>
       <c r="C175">
         <v>909</v>
@@ -13939,7 +14475,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="C176">
         <v>659</v>
@@ -14013,7 +14549,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>116</v>
+        <v>190</v>
       </c>
       <c r="C177">
         <v>702</v>
@@ -14087,7 +14623,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="C178">
         <v>812</v>
@@ -14161,7 +14697,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>118</v>
+        <v>192</v>
       </c>
       <c r="C179">
         <v>1079</v>
@@ -14235,7 +14771,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>119</v>
+        <v>193</v>
       </c>
       <c r="C180">
         <v>974</v>
@@ -14309,7 +14845,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="C181">
         <v>382</v>
@@ -14383,7 +14919,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="C182">
         <v>1128</v>
@@ -14457,7 +14993,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>120</v>
+        <v>196</v>
       </c>
       <c r="C183">
         <v>1139</v>
@@ -14531,7 +15067,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>37</v>
+        <v>197</v>
       </c>
       <c r="C184">
         <v>1012</v>
@@ -14605,7 +15141,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="C185">
         <v>723</v>
@@ -14679,7 +15215,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="C186">
         <v>616</v>
@@ -14753,7 +15289,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="C187">
         <v>462</v>
@@ -14827,7 +15363,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>69</v>
+        <v>201</v>
       </c>
       <c r="C188">
         <v>791</v>
@@ -14901,7 +15437,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="C189">
         <v>797</v>
@@ -14975,7 +15511,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>124</v>
+        <v>203</v>
       </c>
       <c r="C190">
         <v>964</v>
@@ -15049,7 +15585,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="C191">
         <v>825</v>
@@ -15123,7 +15659,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="C192">
         <v>912</v>
@@ -15197,7 +15733,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>122</v>
+        <v>206</v>
       </c>
       <c r="C193">
         <v>683</v>
@@ -15271,7 +15807,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="C194">
         <v>1159</v>
@@ -15345,7 +15881,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>128</v>
+        <v>208</v>
       </c>
       <c r="C195">
         <v>1091</v>
@@ -15419,7 +15955,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>129</v>
+        <v>208</v>
       </c>
       <c r="C196">
         <v>502</v>
@@ -15493,7 +16029,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="C197">
         <v>700</v>
@@ -15567,7 +16103,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>131</v>
+        <v>210</v>
       </c>
       <c r="C198">
         <v>636</v>
@@ -15641,7 +16177,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>132</v>
+        <v>211</v>
       </c>
       <c r="C199">
         <v>1040</v>
@@ -15715,7 +16251,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>133</v>
+        <v>212</v>
       </c>
       <c r="C200">
         <v>879</v>
@@ -15789,7 +16325,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="C201">
         <v>998</v>
@@ -15863,7 +16399,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>37</v>
+        <v>214</v>
       </c>
       <c r="C202">
         <v>543</v>
@@ -15937,7 +16473,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>14</v>
+        <v>215</v>
       </c>
       <c r="C203">
         <v>1060</v>
@@ -16011,7 +16547,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>135</v>
+        <v>216</v>
       </c>
       <c r="C204">
         <v>896</v>
@@ -16085,7 +16621,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="C205">
         <v>909</v>
@@ -16159,7 +16695,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>137</v>
+        <v>218</v>
       </c>
       <c r="C206">
         <v>733</v>
@@ -16233,7 +16769,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>66</v>
+        <v>219</v>
       </c>
       <c r="C207">
         <v>232</v>
@@ -16307,7 +16843,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>138</v>
+        <v>219</v>
       </c>
       <c r="C208">
         <v>775</v>
@@ -16381,7 +16917,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="C209">
         <v>446</v>
@@ -16455,7 +16991,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="C210">
         <v>953</v>
@@ -16529,7 +17065,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>141</v>
+        <v>221</v>
       </c>
       <c r="C211">
         <v>714</v>
@@ -16603,7 +17139,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>142</v>
+        <v>222</v>
       </c>
       <c r="C212">
         <v>746</v>
@@ -16677,7 +17213,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="C213">
         <v>880</v>
@@ -16751,7 +17287,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>13</v>
+        <v>224</v>
       </c>
       <c r="C214">
         <v>673</v>
@@ -16825,7 +17361,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>144</v>
+        <v>225</v>
       </c>
       <c r="C215">
         <v>755</v>
@@ -16899,7 +17435,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>145</v>
+        <v>226</v>
       </c>
       <c r="C216">
         <v>1139</v>
@@ -16973,7 +17509,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="C217">
         <v>854</v>
@@ -17047,7 +17583,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>147</v>
+        <v>228</v>
       </c>
       <c r="C218">
         <v>1148</v>
@@ -17121,7 +17657,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>148</v>
+        <v>229</v>
       </c>
       <c r="C219">
         <v>1078</v>
@@ -17195,7 +17731,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="C220">
         <v>879</v>
@@ -17269,7 +17805,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>148</v>
+        <v>231</v>
       </c>
       <c r="C221">
         <v>765</v>
@@ -17343,7 +17879,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>145</v>
+        <v>232</v>
       </c>
       <c r="C222">
         <v>868</v>
@@ -17417,7 +17953,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>148</v>
+        <v>233</v>
       </c>
       <c r="C223">
         <v>993</v>
@@ -17491,7 +18027,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>37</v>
+        <v>234</v>
       </c>
       <c r="C224">
         <v>851</v>
@@ -17565,7 +18101,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>149</v>
+        <v>235</v>
       </c>
       <c r="C225">
         <v>815</v>
@@ -17639,7 +18175,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>149</v>
+        <v>236</v>
       </c>
       <c r="C226">
         <v>1006</v>
@@ -17713,7 +18249,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>149</v>
+        <v>237</v>
       </c>
       <c r="C227">
         <v>1036</v>
@@ -17787,7 +18323,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>62</v>
+        <v>238</v>
       </c>
       <c r="C228">
         <v>898</v>
@@ -17861,7 +18397,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>150</v>
+        <v>239</v>
       </c>
       <c r="C229">
         <v>954</v>
@@ -17935,7 +18471,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>121</v>
+        <v>240</v>
       </c>
       <c r="C230">
         <v>884</v>
@@ -18009,7 +18545,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="C231">
         <v>791</v>
@@ -18083,7 +18619,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>122</v>
+        <v>242</v>
       </c>
       <c r="C232">
         <v>981</v>
@@ -18157,7 +18693,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>152</v>
+        <v>243</v>
       </c>
       <c r="C233">
         <v>765</v>
@@ -18231,7 +18767,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>37</v>
+        <v>244</v>
       </c>
       <c r="C234">
         <v>952</v>
@@ -18305,7 +18841,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>145</v>
+        <v>245</v>
       </c>
       <c r="C235">
         <v>965</v>
@@ -18379,7 +18915,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>148</v>
+        <v>246</v>
       </c>
       <c r="C236">
         <v>990</v>
@@ -18453,7 +18989,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>153</v>
+        <v>247</v>
       </c>
       <c r="C237">
         <v>925</v>
@@ -18527,7 +19063,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>154</v>
+        <v>248</v>
       </c>
       <c r="C238">
         <v>656</v>
@@ -18601,7 +19137,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>153</v>
+        <v>249</v>
       </c>
       <c r="C239">
         <v>982</v>
@@ -18675,7 +19211,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>154</v>
+        <v>250</v>
       </c>
       <c r="C240">
         <v>1075</v>
@@ -18749,7 +19285,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>62</v>
+        <v>251</v>
       </c>
       <c r="C241">
         <v>1134</v>
@@ -18823,7 +19359,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>150</v>
+        <v>252</v>
       </c>
       <c r="C242">
         <v>1020</v>
@@ -18897,7 +19433,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>155</v>
+        <v>253</v>
       </c>
       <c r="C243">
         <v>821</v>
@@ -18971,7 +19507,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>156</v>
+        <v>254</v>
       </c>
       <c r="C244">
         <v>805</v>
@@ -19045,7 +19581,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>157</v>
+        <v>255</v>
       </c>
       <c r="C245">
         <v>592</v>
@@ -19119,7 +19655,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>158</v>
+        <v>256</v>
       </c>
       <c r="C246">
         <v>706</v>
@@ -19193,7 +19729,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>159</v>
+        <v>257</v>
       </c>
       <c r="C247">
         <v>655</v>
@@ -19267,7 +19803,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>138</v>
+        <v>258</v>
       </c>
       <c r="C248">
         <v>614</v>
@@ -19341,7 +19877,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>140</v>
+        <v>259</v>
       </c>
       <c r="C249">
         <v>745</v>
@@ -19415,7 +19951,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>143</v>
+        <v>260</v>
       </c>
       <c r="C250">
         <v>761</v>
@@ -19489,7 +20025,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>121</v>
+        <v>261</v>
       </c>
       <c r="C251">
         <v>664</v>
@@ -19563,7 +20099,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>122</v>
+        <v>262</v>
       </c>
       <c r="C252">
         <v>643</v>
@@ -19637,7 +20173,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>160</v>
+        <v>263</v>
       </c>
       <c r="C253">
         <v>908</v>
@@ -19711,7 +20247,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>161</v>
+        <v>264</v>
       </c>
       <c r="C254">
         <v>765</v>
@@ -19785,7 +20321,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>162</v>
+        <v>265</v>
       </c>
       <c r="C255">
         <v>1066</v>
@@ -19859,7 +20395,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>14</v>
+        <v>266</v>
       </c>
       <c r="C256">
         <v>1158</v>
@@ -19933,7 +20469,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>163</v>
+        <v>267</v>
       </c>
       <c r="C257">
         <v>968</v>
@@ -20007,7 +20543,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>164</v>
+        <v>268</v>
       </c>
       <c r="C258">
         <v>912</v>
@@ -20081,7 +20617,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>165</v>
+        <v>269</v>
       </c>
       <c r="C259">
         <v>1046</v>
@@ -20155,7 +20691,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>166</v>
+        <v>270</v>
       </c>
       <c r="C260">
         <v>1019</v>
@@ -20229,7 +20765,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>167</v>
+        <v>271</v>
       </c>
       <c r="C261">
         <v>1053</v>
@@ -20303,7 +20839,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>168</v>
+        <v>272</v>
       </c>
       <c r="C262">
         <v>1014</v>
@@ -20377,7 +20913,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>169</v>
+        <v>273</v>
       </c>
       <c r="C263">
         <v>1102</v>
@@ -20451,7 +20987,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>170</v>
+        <v>274</v>
       </c>
       <c r="C264">
         <v>1017</v>
@@ -20525,7 +21061,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>171</v>
+        <v>275</v>
       </c>
       <c r="C265">
         <v>987</v>
@@ -20599,7 +21135,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
       <c r="C266">
         <v>1066</v>
@@ -20673,7 +21209,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>172</v>
+        <v>277</v>
       </c>
       <c r="C267">
         <v>937</v>
@@ -20747,7 +21283,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>130</v>
+        <v>278</v>
       </c>
       <c r="C268">
         <v>833</v>
@@ -20821,7 +21357,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>131</v>
+        <v>279</v>
       </c>
       <c r="C269">
         <v>790</v>
@@ -20895,7 +21431,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>157</v>
+        <v>279</v>
       </c>
       <c r="C270">
         <v>380</v>
@@ -20969,7 +21505,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>121</v>
+        <v>279</v>
       </c>
       <c r="C271">
         <v>910</v>
@@ -21043,7 +21579,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>122</v>
+        <v>279</v>
       </c>
       <c r="C272">
         <v>642</v>
@@ -21117,7 +21653,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="C273">
         <v>740</v>
@@ -21191,7 +21727,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>143</v>
+        <v>281</v>
       </c>
       <c r="C274">
         <v>722</v>
@@ -21265,7 +21801,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>173</v>
+        <v>282</v>
       </c>
       <c r="C275">
         <v>641</v>
@@ -21339,7 +21875,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>174</v>
+        <v>283</v>
       </c>
       <c r="C276">
         <v>619</v>
@@ -21413,7 +21949,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>37</v>
+        <v>284</v>
       </c>
       <c r="C277">
         <v>981</v>
@@ -21487,7 +22023,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>157</v>
+        <v>285</v>
       </c>
       <c r="C278">
         <v>729</v>
@@ -21561,7 +22097,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>13</v>
+        <v>286</v>
       </c>
       <c r="C279">
         <v>389</v>
@@ -21635,7 +22171,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>175</v>
+        <v>287</v>
       </c>
       <c r="C280">
         <v>595</v>
@@ -21709,7 +22245,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>153</v>
+        <v>288</v>
       </c>
       <c r="C281">
         <v>621</v>
@@ -21783,7 +22319,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>154</v>
+        <v>289</v>
       </c>
       <c r="C282">
         <v>595</v>
@@ -21857,7 +22393,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>176</v>
+        <v>289</v>
       </c>
       <c r="C283">
         <v>808</v>
@@ -21931,7 +22467,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>13</v>
+        <v>290</v>
       </c>
       <c r="C284">
         <v>1033</v>
@@ -22005,7 +22541,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>13</v>
+        <v>290</v>
       </c>
       <c r="C285">
         <v>888</v>
@@ -22079,7 +22615,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>138</v>
+        <v>291</v>
       </c>
       <c r="C286">
         <v>751</v>
@@ -22153,7 +22689,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>13</v>
+        <v>292</v>
       </c>
       <c r="C287">
         <v>340</v>
@@ -22227,7 +22763,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>155</v>
+        <v>293</v>
       </c>
       <c r="C288">
         <v>1105</v>
@@ -22301,7 +22837,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>156</v>
+        <v>294</v>
       </c>
       <c r="C289">
         <v>1121</v>
@@ -22375,7 +22911,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>177</v>
+        <v>295</v>
       </c>
       <c r="C290">
         <v>671</v>
@@ -22449,7 +22985,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>178</v>
+        <v>296</v>
       </c>
       <c r="C291">
         <v>764</v>
@@ -22523,7 +23059,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>179</v>
+        <v>297</v>
       </c>
       <c r="C292">
         <v>892</v>
@@ -22597,7 +23133,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>180</v>
+        <v>298</v>
       </c>
       <c r="C293">
         <v>950</v>
@@ -22671,7 +23207,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>96</v>
+        <v>298</v>
       </c>
       <c r="C294">
         <v>1012</v>
@@ -22745,7 +23281,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>97</v>
+        <v>299</v>
       </c>
       <c r="C295">
         <v>836</v>
@@ -22819,7 +23355,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>97</v>
+        <v>300</v>
       </c>
       <c r="C296">
         <v>857</v>
@@ -22893,7 +23429,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>181</v>
+        <v>301</v>
       </c>
       <c r="C297">
         <v>800</v>
@@ -22967,7 +23503,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>181</v>
+        <v>302</v>
       </c>
       <c r="C298">
         <v>713</v>
@@ -23041,7 +23577,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>182</v>
+        <v>303</v>
       </c>
       <c r="C299">
         <v>804</v>
@@ -23115,7 +23651,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>92</v>
+        <v>304</v>
       </c>
       <c r="C300">
         <v>856</v>
@@ -23189,7 +23725,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>138</v>
+        <v>305</v>
       </c>
       <c r="C301">
         <v>906</v>
@@ -23263,7 +23799,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>14</v>
+        <v>306</v>
       </c>
       <c r="C302">
         <v>618</v>
@@ -23337,7 +23873,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>121</v>
+        <v>307</v>
       </c>
       <c r="C303">
         <v>1151</v>
@@ -23411,7 +23947,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>183</v>
+        <v>308</v>
       </c>
       <c r="C304">
         <v>1103</v>
@@ -23485,7 +24021,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>184</v>
+        <v>309</v>
       </c>
       <c r="C305">
         <v>1138</v>
@@ -23559,7 +24095,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>122</v>
+        <v>310</v>
       </c>
       <c r="C306">
         <v>1132</v>
@@ -23633,7 +24169,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>185</v>
+        <v>311</v>
       </c>
       <c r="C307">
         <v>664</v>
@@ -23707,7 +24243,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>186</v>
+        <v>312</v>
       </c>
       <c r="C308">
         <v>638</v>
@@ -23781,7 +24317,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>74</v>
+        <v>313</v>
       </c>
       <c r="C309">
         <v>833</v>
@@ -23855,7 +24391,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>75</v>
+        <v>314</v>
       </c>
       <c r="C310">
         <v>740</v>
@@ -23929,7 +24465,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>96</v>
+        <v>315</v>
       </c>
       <c r="C311">
         <v>820</v>
@@ -24003,7 +24539,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>97</v>
+        <v>316</v>
       </c>
       <c r="C312">
         <v>720</v>
@@ -24077,7 +24613,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>187</v>
+        <v>317</v>
       </c>
       <c r="C313">
         <v>1011</v>
@@ -24151,7 +24687,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>188</v>
+        <v>318</v>
       </c>
       <c r="C314">
         <v>993</v>
@@ -24225,7 +24761,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>187</v>
+        <v>319</v>
       </c>
       <c r="C315">
         <v>1051</v>
@@ -24299,7 +24835,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>163</v>
+        <v>320</v>
       </c>
       <c r="C316">
         <v>1009</v>
@@ -24373,7 +24909,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>189</v>
+        <v>321</v>
       </c>
       <c r="C317">
         <v>660</v>
@@ -24447,7 +24983,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>190</v>
+        <v>322</v>
       </c>
       <c r="C318">
         <v>625</v>
@@ -24521,7 +25057,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>191</v>
+        <v>323</v>
       </c>
       <c r="C319">
         <v>1046</v>
@@ -24595,7 +25131,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>192</v>
+        <v>324</v>
       </c>
       <c r="C320">
         <v>827</v>
@@ -24669,7 +25205,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>193</v>
+        <v>325</v>
       </c>
       <c r="C321">
         <v>848</v>
@@ -24743,7 +25279,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>194</v>
+        <v>326</v>
       </c>
       <c r="C322">
         <v>772</v>
@@ -24817,7 +25353,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>195</v>
+        <v>327</v>
       </c>
       <c r="C323">
         <v>957</v>
@@ -24891,7 +25427,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>18</v>
+        <v>328</v>
       </c>
       <c r="C324">
         <v>946</v>
@@ -24965,7 +25501,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>196</v>
+        <v>329</v>
       </c>
       <c r="C325">
         <v>608</v>
@@ -25039,7 +25575,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>157</v>
+        <v>330</v>
       </c>
       <c r="C326">
         <v>1073</v>
@@ -25113,7 +25649,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>13</v>
+        <v>331</v>
       </c>
       <c r="C327">
         <v>1068</v>
@@ -25187,7 +25723,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>197</v>
+        <v>332</v>
       </c>
       <c r="C328">
         <v>1125</v>
@@ -25261,7 +25797,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>198</v>
+        <v>333</v>
       </c>
       <c r="C329">
         <v>1091</v>
@@ -25335,7 +25871,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>199</v>
+        <v>334</v>
       </c>
       <c r="C330">
         <v>1012</v>
@@ -25409,7 +25945,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>200</v>
+        <v>335</v>
       </c>
       <c r="C331">
         <v>1075</v>
@@ -25483,7 +26019,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="C332">
         <v>1118</v>
@@ -25557,7 +26093,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>201</v>
+        <v>337</v>
       </c>
       <c r="C333">
         <v>580</v>
@@ -25631,7 +26167,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>37</v>
+        <v>338</v>
       </c>
       <c r="C334">
         <v>504</v>
@@ -25705,7 +26241,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>202</v>
+        <v>339</v>
       </c>
       <c r="C335">
         <v>642</v>
@@ -25779,7 +26315,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>203</v>
+        <v>340</v>
       </c>
       <c r="C336">
         <v>645</v>
@@ -25853,7 +26389,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>204</v>
+        <v>341</v>
       </c>
       <c r="C337">
         <v>596</v>
@@ -25927,7 +26463,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>205</v>
+        <v>342</v>
       </c>
       <c r="C338">
         <v>961</v>
@@ -26001,7 +26537,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>206</v>
+        <v>343</v>
       </c>
       <c r="C339">
         <v>738</v>
@@ -26075,7 +26611,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>207</v>
+        <v>344</v>
       </c>
       <c r="C340">
         <v>830</v>
@@ -26149,7 +26685,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>208</v>
+        <v>345</v>
       </c>
       <c r="C341">
         <v>668</v>
@@ -26223,7 +26759,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>209</v>
+        <v>346</v>
       </c>
       <c r="C342">
         <v>1160</v>
@@ -26297,7 +26833,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>64</v>
+        <v>347</v>
       </c>
       <c r="C343">
         <v>735</v>
@@ -26371,7 +26907,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>155</v>
+        <v>348</v>
       </c>
       <c r="C344">
         <v>1097</v>
@@ -26445,7 +26981,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>177</v>
+        <v>349</v>
       </c>
       <c r="C345">
         <v>1155</v>
@@ -26519,7 +27055,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>156</v>
+        <v>350</v>
       </c>
       <c r="C346">
         <v>1154</v>
@@ -26593,7 +27129,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>37</v>
+        <v>351</v>
       </c>
       <c r="C347">
         <v>693</v>
@@ -26667,7 +27203,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>14</v>
+        <v>352</v>
       </c>
       <c r="C348">
         <v>297</v>
@@ -26741,7 +27277,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>210</v>
+        <v>353</v>
       </c>
       <c r="C349">
         <v>528</v>
@@ -26815,7 +27351,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>211</v>
+        <v>354</v>
       </c>
       <c r="C350">
         <v>885</v>
@@ -26889,7 +27425,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>212</v>
+        <v>355</v>
       </c>
       <c r="C351">
         <v>753</v>
@@ -26963,7 +27499,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>65</v>
+        <v>356</v>
       </c>
       <c r="C352">
         <v>503</v>
@@ -27037,7 +27573,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>18</v>
+        <v>357</v>
       </c>
       <c r="C353">
         <v>575</v>
@@ -27111,7 +27647,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>52</v>
+        <v>358</v>
       </c>
       <c r="C354">
         <v>720</v>
@@ -27185,7 +27721,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>53</v>
+        <v>359</v>
       </c>
       <c r="C355">
         <v>785</v>
